--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/post DDV_HRM-2031-0180/Panel-28/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/post DDV_HRM-2031-0180/Panel-28/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.21616</v>
+        <v>16.9678</v>
       </c>
       <c r="D2" t="n">
-        <v>16.6566</v>
+        <v>16.70733</v>
       </c>
       <c r="E2" t="n">
-        <v>17.26887</v>
+        <v>16.87249</v>
       </c>
       <c r="F2" t="n">
-        <v>42.85791</v>
+        <v>43.8119</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05206</v>
+        <v>0.05158</v>
       </c>
       <c r="H2" t="n">
-        <v>1.84272</v>
+        <v>1.84078</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.12164</v>
+        <v>16.90214</v>
       </c>
       <c r="D3" t="n">
-        <v>16.68882</v>
+        <v>16.7023</v>
       </c>
       <c r="E3" t="n">
-        <v>16.89536</v>
+        <v>16.85324</v>
       </c>
       <c r="F3" t="n">
-        <v>42.61574</v>
+        <v>43.76973</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05039</v>
+        <v>0.05192</v>
       </c>
       <c r="H3" t="n">
-        <v>1.82537</v>
+        <v>1.80418</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.82095</v>
+        <v>16.90142</v>
       </c>
       <c r="D4" t="n">
-        <v>17.14779</v>
+        <v>16.58835</v>
       </c>
       <c r="E4" t="n">
-        <v>16.82376</v>
+        <v>16.81071</v>
       </c>
       <c r="F4" t="n">
-        <v>43.03328</v>
+        <v>42.09608</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05158</v>
+        <v>0.05141</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83009</v>
+        <v>1.8297</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.68257</v>
+        <v>16.77574</v>
       </c>
       <c r="D6" t="n">
-        <v>15.89134</v>
+        <v>16.14041</v>
       </c>
       <c r="E6" t="n">
-        <v>16.56782</v>
+        <v>16.74226</v>
       </c>
       <c r="F6" t="n">
-        <v>22.42151</v>
+        <v>21.77164</v>
       </c>
       <c r="G6" t="n">
-        <v>34.58265</v>
+        <v>34.8287</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.47922</v>
+        <v>16.76835</v>
       </c>
       <c r="D7" t="n">
-        <v>16.33923</v>
+        <v>15.84698</v>
       </c>
       <c r="E7" t="n">
-        <v>16.13427</v>
+        <v>16.57575</v>
       </c>
       <c r="F7" t="n">
-        <v>22.12017</v>
+        <v>21.99169</v>
       </c>
       <c r="G7" t="n">
-        <v>34.95235</v>
+        <v>34.61926</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.77804</v>
+        <v>16.86371</v>
       </c>
       <c r="D8" t="n">
-        <v>16.40447</v>
+        <v>16.29399</v>
       </c>
       <c r="E8" t="n">
-        <v>16.68247</v>
+        <v>16.82941</v>
       </c>
       <c r="F8" t="n">
-        <v>21.79214</v>
+        <v>22.07599</v>
       </c>
       <c r="G8" t="n">
-        <v>34.56931</v>
+        <v>34.76269</v>
       </c>
     </row>
   </sheetData>
